--- a/DashboardSaleAI.xlsx
+++ b/DashboardSaleAI.xlsx
@@ -8,16 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\Sale\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FCEDCD-544A-44DC-812A-3AB5B036B13B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0B5B3F-FB39-42E2-92F9-68B956D60376}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" activeTab="1" xr2:uid="{51F89FC5-9E8B-4444-B8E4-5BD9F41461A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" activeTab="4" xr2:uid="{51F89FC5-9E8B-4444-B8E4-5BD9F41461A1}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
     <sheet name="2025" sheetId="2" r:id="rId2"/>
     <sheet name="PLAN2026" sheetId="3" r:id="rId3"/>
     <sheet name="Status" sheetId="4" r:id="rId4"/>
+    <sheet name="CPAC2026" sheetId="8" r:id="rId5"/>
+    <sheet name="PLANCPAC2026" sheetId="9" r:id="rId6"/>
+    <sheet name="CPAC2025" sheetId="10" r:id="rId7"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId8"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025'!$A$1:$S$287</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$A$1:$S$291</definedName>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4987" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5044" uniqueCount="791">
   <si>
     <t>กิจการ</t>
   </si>
@@ -2417,7 +2423,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="#,##0;\-;\-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2455,6 +2461,11 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2551,13 +2562,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2691,10 +2703,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="4" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{BA9139B0-AFD5-4753-A17F-CFBB11C17E24}"/>
     <cellStyle name="Normal_FC Type S -Update มิ.ย.54" xfId="3" xr:uid="{4311FE94-9E7B-4DC1-A9E8-964CD256E021}"/>
     <cellStyle name="Normal_ยอดผลิต jan-16 dec" xfId="2" xr:uid="{05FFCB47-9425-4128-A319-DAAEE2BC1E11}"/>
   </cellStyles>
@@ -2709,6 +2724,1387 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="CPAC 2026-WEB"/>
+      <sheetName val="CPAC 2025-WEB"/>
+      <sheetName val="data"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="C1" t="str">
+            <v>ปี 2026(ขนาดจิ๋ว, ขนาดเล็ก, ขนาดกลาง, ขนาดใหญ่, ขนาดเมก้า)</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="C2" t="str">
+            <v>มกราคม</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>กุมภาพันธ์</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>มีนาคม</v>
+          </cell>
+          <cell r="I2" t="str">
+            <v>เมษายน</v>
+          </cell>
+          <cell r="K2" t="str">
+            <v>พฤษภาคม</v>
+          </cell>
+          <cell r="M2" t="str">
+            <v>มิถุนายน</v>
+          </cell>
+          <cell r="O2" t="str">
+            <v>กรกฎาคม</v>
+          </cell>
+          <cell r="Q2" t="str">
+            <v>สิงหาคม</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="H3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="I3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="J3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="K3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="L3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="M3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="N3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="O3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="P3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="Q3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="R3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="S3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="T3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="U3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="V3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="W3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="X3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+          <cell r="Y3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="Z3" t="str">
+            <v>เทียบเป้าหมาย</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="I4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="J4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="K4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="L4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="M4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="N4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="O4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="P4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="Q4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="R4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="S4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="T4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="U4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="V4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="W4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="X4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="Y4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="Z4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>1-Metro</v>
+          </cell>
+          <cell r="C5">
+            <v>190200</v>
+          </cell>
+          <cell r="D5">
+            <v>214300</v>
+          </cell>
+          <cell r="E5">
+            <v>219954</v>
+          </cell>
+          <cell r="F5">
+            <v>239200</v>
+          </cell>
+          <cell r="G5">
+            <v>260272</v>
+          </cell>
+          <cell r="H5">
+            <v>265100</v>
+          </cell>
+          <cell r="I5">
+            <v>192174</v>
+          </cell>
+          <cell r="J5">
+            <v>175100</v>
+          </cell>
+          <cell r="K5">
+            <v>214257</v>
+          </cell>
+          <cell r="L5">
+            <v>211400</v>
+          </cell>
+          <cell r="M5">
+            <v>208327</v>
+          </cell>
+          <cell r="N5">
+            <v>234300</v>
+          </cell>
+          <cell r="O5">
+            <v>219159</v>
+          </cell>
+          <cell r="P5">
+            <v>239300</v>
+          </cell>
+          <cell r="Q5">
+            <v>215373</v>
+          </cell>
+          <cell r="R5">
+            <v>214500</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>190200</v>
+          </cell>
+          <cell r="D6">
+            <v>214300</v>
+          </cell>
+          <cell r="E6">
+            <v>219954</v>
+          </cell>
+          <cell r="F6">
+            <v>239200</v>
+          </cell>
+          <cell r="G6">
+            <v>260272</v>
+          </cell>
+          <cell r="H6">
+            <v>265100</v>
+          </cell>
+          <cell r="I6">
+            <v>192174</v>
+          </cell>
+          <cell r="J6">
+            <v>175100</v>
+          </cell>
+          <cell r="K6">
+            <v>214257</v>
+          </cell>
+          <cell r="L6">
+            <v>211400</v>
+          </cell>
+          <cell r="M6">
+            <v>208327</v>
+          </cell>
+          <cell r="N6">
+            <v>234300</v>
+          </cell>
+          <cell r="O6">
+            <v>219159</v>
+          </cell>
+          <cell r="P6">
+            <v>239300</v>
+          </cell>
+          <cell r="Q6">
+            <v>215373</v>
+          </cell>
+          <cell r="R6">
+            <v>214500</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>2-East</v>
+          </cell>
+          <cell r="C7">
+            <v>160382</v>
+          </cell>
+          <cell r="D7">
+            <v>149850</v>
+          </cell>
+          <cell r="E7">
+            <v>171181</v>
+          </cell>
+          <cell r="F7">
+            <v>158950</v>
+          </cell>
+          <cell r="G7">
+            <v>193873</v>
+          </cell>
+          <cell r="H7">
+            <v>175470</v>
+          </cell>
+          <cell r="I7">
+            <v>131725</v>
+          </cell>
+          <cell r="J7">
+            <v>136800</v>
+          </cell>
+          <cell r="K7">
+            <v>156343</v>
+          </cell>
+          <cell r="L7">
+            <v>169370</v>
+          </cell>
+          <cell r="M7">
+            <v>161950</v>
+          </cell>
+          <cell r="N7">
+            <v>178420</v>
+          </cell>
+          <cell r="O7">
+            <v>175011</v>
+          </cell>
+          <cell r="P7">
+            <v>184340</v>
+          </cell>
+          <cell r="Q7">
+            <v>183407</v>
+          </cell>
+          <cell r="R7">
+            <v>185770</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>160382</v>
+          </cell>
+          <cell r="D8">
+            <v>149850</v>
+          </cell>
+          <cell r="E8">
+            <v>171181</v>
+          </cell>
+          <cell r="F8">
+            <v>158950</v>
+          </cell>
+          <cell r="G8">
+            <v>193873</v>
+          </cell>
+          <cell r="H8">
+            <v>175470</v>
+          </cell>
+          <cell r="I8">
+            <v>131725</v>
+          </cell>
+          <cell r="J8">
+            <v>136800</v>
+          </cell>
+          <cell r="K8">
+            <v>156343</v>
+          </cell>
+          <cell r="L8">
+            <v>169370</v>
+          </cell>
+          <cell r="M8">
+            <v>161950</v>
+          </cell>
+          <cell r="N8">
+            <v>178420</v>
+          </cell>
+          <cell r="O8">
+            <v>175011</v>
+          </cell>
+          <cell r="P8">
+            <v>184340</v>
+          </cell>
+          <cell r="Q8">
+            <v>183407</v>
+          </cell>
+          <cell r="R8">
+            <v>185770</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>3-West</v>
+          </cell>
+          <cell r="C9">
+            <v>86684</v>
+          </cell>
+          <cell r="D9">
+            <v>83500</v>
+          </cell>
+          <cell r="E9">
+            <v>102154</v>
+          </cell>
+          <cell r="F9">
+            <v>88000</v>
+          </cell>
+          <cell r="G9">
+            <v>115805</v>
+          </cell>
+          <cell r="H9">
+            <v>95100</v>
+          </cell>
+          <cell r="I9">
+            <v>80877</v>
+          </cell>
+          <cell r="J9">
+            <v>73700</v>
+          </cell>
+          <cell r="K9">
+            <v>98781</v>
+          </cell>
+          <cell r="L9">
+            <v>96200</v>
+          </cell>
+          <cell r="M9">
+            <v>90261</v>
+          </cell>
+          <cell r="N9">
+            <v>91700</v>
+          </cell>
+          <cell r="O9">
+            <v>105339</v>
+          </cell>
+          <cell r="P9">
+            <v>96500</v>
+          </cell>
+          <cell r="Q9">
+            <v>94434</v>
+          </cell>
+          <cell r="R9">
+            <v>93200</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>86684</v>
+          </cell>
+          <cell r="D10">
+            <v>83500</v>
+          </cell>
+          <cell r="E10">
+            <v>102154</v>
+          </cell>
+          <cell r="F10">
+            <v>88000</v>
+          </cell>
+          <cell r="G10">
+            <v>115805</v>
+          </cell>
+          <cell r="H10">
+            <v>95100</v>
+          </cell>
+          <cell r="I10">
+            <v>80877</v>
+          </cell>
+          <cell r="J10">
+            <v>73700</v>
+          </cell>
+          <cell r="K10">
+            <v>98781</v>
+          </cell>
+          <cell r="L10">
+            <v>96200</v>
+          </cell>
+          <cell r="M10">
+            <v>90261</v>
+          </cell>
+          <cell r="N10">
+            <v>91700</v>
+          </cell>
+          <cell r="O10">
+            <v>105339</v>
+          </cell>
+          <cell r="P10">
+            <v>96500</v>
+          </cell>
+          <cell r="Q10">
+            <v>94434</v>
+          </cell>
+          <cell r="R10">
+            <v>93200</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>5-NorthE</v>
+          </cell>
+          <cell r="C11">
+            <v>69073</v>
+          </cell>
+          <cell r="D11">
+            <v>83225</v>
+          </cell>
+          <cell r="E11">
+            <v>73598</v>
+          </cell>
+          <cell r="F11">
+            <v>83925</v>
+          </cell>
+          <cell r="G11">
+            <v>99432</v>
+          </cell>
+          <cell r="H11">
+            <v>92889</v>
+          </cell>
+          <cell r="I11">
+            <v>68047</v>
+          </cell>
+          <cell r="J11">
+            <v>76954</v>
+          </cell>
+          <cell r="K11">
+            <v>67717</v>
+          </cell>
+          <cell r="L11">
+            <v>84370</v>
+          </cell>
+          <cell r="M11">
+            <v>70374</v>
+          </cell>
+          <cell r="N11">
+            <v>84225</v>
+          </cell>
+          <cell r="O11">
+            <v>73141</v>
+          </cell>
+          <cell r="P11">
+            <v>86925</v>
+          </cell>
+          <cell r="Q11">
+            <v>66304</v>
+          </cell>
+          <cell r="R11">
+            <v>87025</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>69073</v>
+          </cell>
+          <cell r="D12">
+            <v>83225</v>
+          </cell>
+          <cell r="E12">
+            <v>73598</v>
+          </cell>
+          <cell r="F12">
+            <v>83925</v>
+          </cell>
+          <cell r="G12">
+            <v>99432</v>
+          </cell>
+          <cell r="H12">
+            <v>92889</v>
+          </cell>
+          <cell r="I12">
+            <v>68047</v>
+          </cell>
+          <cell r="J12">
+            <v>76954</v>
+          </cell>
+          <cell r="K12">
+            <v>67717</v>
+          </cell>
+          <cell r="L12">
+            <v>84370</v>
+          </cell>
+          <cell r="M12">
+            <v>70374</v>
+          </cell>
+          <cell r="N12">
+            <v>84225</v>
+          </cell>
+          <cell r="O12">
+            <v>73141</v>
+          </cell>
+          <cell r="P12">
+            <v>86925</v>
+          </cell>
+          <cell r="Q12">
+            <v>66304</v>
+          </cell>
+          <cell r="R12">
+            <v>87025</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>6-South</v>
+          </cell>
+          <cell r="C13">
+            <v>90495</v>
+          </cell>
+          <cell r="D13">
+            <v>93800</v>
+          </cell>
+          <cell r="E13">
+            <v>87159</v>
+          </cell>
+          <cell r="F13">
+            <v>94700</v>
+          </cell>
+          <cell r="G13">
+            <v>100721</v>
+          </cell>
+          <cell r="H13">
+            <v>107900</v>
+          </cell>
+          <cell r="I13">
+            <v>74766</v>
+          </cell>
+          <cell r="J13">
+            <v>91600</v>
+          </cell>
+          <cell r="K13">
+            <v>85556</v>
+          </cell>
+          <cell r="L13">
+            <v>104000</v>
+          </cell>
+          <cell r="M13">
+            <v>88261</v>
+          </cell>
+          <cell r="N13">
+            <v>102200</v>
+          </cell>
+          <cell r="O13">
+            <v>90419</v>
+          </cell>
+          <cell r="P13">
+            <v>103800</v>
+          </cell>
+          <cell r="Q13">
+            <v>99113</v>
+          </cell>
+          <cell r="R13">
+            <v>100900</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>90495</v>
+          </cell>
+          <cell r="D14">
+            <v>93800</v>
+          </cell>
+          <cell r="E14">
+            <v>87159</v>
+          </cell>
+          <cell r="F14">
+            <v>94700</v>
+          </cell>
+          <cell r="G14">
+            <v>100721</v>
+          </cell>
+          <cell r="H14">
+            <v>107900</v>
+          </cell>
+          <cell r="I14">
+            <v>74766</v>
+          </cell>
+          <cell r="J14">
+            <v>91600</v>
+          </cell>
+          <cell r="K14">
+            <v>85556</v>
+          </cell>
+          <cell r="L14">
+            <v>104000</v>
+          </cell>
+          <cell r="M14">
+            <v>88261</v>
+          </cell>
+          <cell r="N14">
+            <v>102200</v>
+          </cell>
+          <cell r="O14">
+            <v>90419</v>
+          </cell>
+          <cell r="P14">
+            <v>103800</v>
+          </cell>
+          <cell r="Q14">
+            <v>99113</v>
+          </cell>
+          <cell r="R14">
+            <v>100900</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>4-North</v>
+          </cell>
+          <cell r="C15">
+            <v>92632</v>
+          </cell>
+          <cell r="D15">
+            <v>97150</v>
+          </cell>
+          <cell r="E15">
+            <v>95678</v>
+          </cell>
+          <cell r="F15">
+            <v>99150</v>
+          </cell>
+          <cell r="G15">
+            <v>112490</v>
+          </cell>
+          <cell r="H15">
+            <v>113800</v>
+          </cell>
+          <cell r="I15">
+            <v>73709</v>
+          </cell>
+          <cell r="J15">
+            <v>80600</v>
+          </cell>
+          <cell r="K15">
+            <v>103374</v>
+          </cell>
+          <cell r="L15">
+            <v>96300</v>
+          </cell>
+          <cell r="M15">
+            <v>100869</v>
+          </cell>
+          <cell r="N15">
+            <v>100400</v>
+          </cell>
+          <cell r="O15">
+            <v>92912</v>
+          </cell>
+          <cell r="P15">
+            <v>100550</v>
+          </cell>
+          <cell r="Q15">
+            <v>98607</v>
+          </cell>
+          <cell r="R15">
+            <v>94100</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>92632</v>
+          </cell>
+          <cell r="D16">
+            <v>97150</v>
+          </cell>
+          <cell r="E16">
+            <v>95678</v>
+          </cell>
+          <cell r="F16">
+            <v>99150</v>
+          </cell>
+          <cell r="G16">
+            <v>112490</v>
+          </cell>
+          <cell r="H16">
+            <v>113800</v>
+          </cell>
+          <cell r="I16">
+            <v>73709</v>
+          </cell>
+          <cell r="J16">
+            <v>80600</v>
+          </cell>
+          <cell r="K16">
+            <v>103374</v>
+          </cell>
+          <cell r="L16">
+            <v>96300</v>
+          </cell>
+          <cell r="M16">
+            <v>100869</v>
+          </cell>
+          <cell r="N16">
+            <v>100400</v>
+          </cell>
+          <cell r="O16">
+            <v>92912</v>
+          </cell>
+          <cell r="P16">
+            <v>100550</v>
+          </cell>
+          <cell r="Q16">
+            <v>98607</v>
+          </cell>
+          <cell r="R16">
+            <v>94100</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>689466</v>
+          </cell>
+          <cell r="D17">
+            <v>721825</v>
+          </cell>
+          <cell r="E17">
+            <v>749724</v>
+          </cell>
+          <cell r="F17">
+            <v>763925</v>
+          </cell>
+          <cell r="G17">
+            <v>882593</v>
+          </cell>
+          <cell r="H17">
+            <v>850259</v>
+          </cell>
+          <cell r="I17">
+            <v>621298</v>
+          </cell>
+          <cell r="J17">
+            <v>634754</v>
+          </cell>
+          <cell r="K17">
+            <v>726027</v>
+          </cell>
+          <cell r="L17">
+            <v>761640</v>
+          </cell>
+          <cell r="M17">
+            <v>720042</v>
+          </cell>
+          <cell r="N17">
+            <v>791245</v>
+          </cell>
+          <cell r="O17">
+            <v>755980</v>
+          </cell>
+          <cell r="P17">
+            <v>811415</v>
+          </cell>
+          <cell r="Q17">
+            <v>757238</v>
+          </cell>
+          <cell r="R17">
+            <v>775495</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>689466</v>
+          </cell>
+          <cell r="D18">
+            <v>721825</v>
+          </cell>
+          <cell r="E18">
+            <v>749724</v>
+          </cell>
+          <cell r="F18">
+            <v>763925</v>
+          </cell>
+          <cell r="G18">
+            <v>882593</v>
+          </cell>
+          <cell r="H18">
+            <v>850259</v>
+          </cell>
+          <cell r="I18">
+            <v>621298</v>
+          </cell>
+          <cell r="J18">
+            <v>634754</v>
+          </cell>
+          <cell r="K18">
+            <v>726027</v>
+          </cell>
+          <cell r="L18">
+            <v>761640</v>
+          </cell>
+          <cell r="M18">
+            <v>720042</v>
+          </cell>
+          <cell r="N18">
+            <v>791245</v>
+          </cell>
+          <cell r="O18">
+            <v>755980</v>
+          </cell>
+          <cell r="P18">
+            <v>811415</v>
+          </cell>
+          <cell r="Q18">
+            <v>757238</v>
+          </cell>
+          <cell r="R18">
+            <v>775495</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="C1" t="str">
+            <v>ปี 2025(ขนาดจิ๋ว, ขนาดเล็ก, ขนาดกลาง, ขนาดใหญ่, ขนาดเมก้า)</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="C2" t="str">
+            <v>มกราคม</v>
+          </cell>
+          <cell r="E2" t="str">
+            <v>กุมภาพันธ์</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>มีนาคม</v>
+          </cell>
+          <cell r="I2" t="str">
+            <v>เมษายน</v>
+          </cell>
+          <cell r="K2" t="str">
+            <v>พฤษภาคม</v>
+          </cell>
+          <cell r="M2" t="str">
+            <v>มิถุนายน</v>
+          </cell>
+          <cell r="O2" t="str">
+            <v>กรกฎาคม</v>
+          </cell>
+          <cell r="Q2" t="str">
+            <v>สิงหาคม</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="E3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="I3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="K3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="M3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="O3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+          <cell r="Q3" t="str">
+            <v>Vol.(m³)</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="C4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="E4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="I4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="K4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="M4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="O4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+          <cell r="Q4" t="str">
+            <v>รวม(m³)</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>1-Metro</v>
+          </cell>
+          <cell r="C5">
+            <v>200099</v>
+          </cell>
+          <cell r="E5">
+            <v>208536</v>
+          </cell>
+          <cell r="G5">
+            <v>239658</v>
+          </cell>
+          <cell r="I5">
+            <v>175649</v>
+          </cell>
+          <cell r="K5">
+            <v>212577</v>
+          </cell>
+          <cell r="M5">
+            <v>236605</v>
+          </cell>
+          <cell r="O5">
+            <v>228963</v>
+          </cell>
+          <cell r="Q5">
+            <v>232783</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="C6">
+            <v>200099</v>
+          </cell>
+          <cell r="E6">
+            <v>208536</v>
+          </cell>
+          <cell r="G6">
+            <v>239658</v>
+          </cell>
+          <cell r="I6">
+            <v>175649</v>
+          </cell>
+          <cell r="K6">
+            <v>212577</v>
+          </cell>
+          <cell r="M6">
+            <v>236605</v>
+          </cell>
+          <cell r="O6">
+            <v>228963</v>
+          </cell>
+          <cell r="Q6">
+            <v>232783</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>2-East</v>
+          </cell>
+          <cell r="C7">
+            <v>174828</v>
+          </cell>
+          <cell r="E7">
+            <v>165963</v>
+          </cell>
+          <cell r="G7">
+            <v>188666</v>
+          </cell>
+          <cell r="I7">
+            <v>138881</v>
+          </cell>
+          <cell r="K7">
+            <v>165051</v>
+          </cell>
+          <cell r="M7">
+            <v>178943</v>
+          </cell>
+          <cell r="O7">
+            <v>201263</v>
+          </cell>
+          <cell r="Q7">
+            <v>184795</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="C8">
+            <v>174828</v>
+          </cell>
+          <cell r="E8">
+            <v>165963</v>
+          </cell>
+          <cell r="G8">
+            <v>188666</v>
+          </cell>
+          <cell r="I8">
+            <v>138881</v>
+          </cell>
+          <cell r="K8">
+            <v>165051</v>
+          </cell>
+          <cell r="M8">
+            <v>178943</v>
+          </cell>
+          <cell r="O8">
+            <v>201263</v>
+          </cell>
+          <cell r="Q8">
+            <v>184795</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>3-West</v>
+          </cell>
+          <cell r="C9">
+            <v>89728</v>
+          </cell>
+          <cell r="E9">
+            <v>100483</v>
+          </cell>
+          <cell r="G9">
+            <v>108389</v>
+          </cell>
+          <cell r="I9">
+            <v>80176</v>
+          </cell>
+          <cell r="K9">
+            <v>86205</v>
+          </cell>
+          <cell r="M9">
+            <v>104123</v>
+          </cell>
+          <cell r="O9">
+            <v>104903</v>
+          </cell>
+          <cell r="Q9">
+            <v>91478</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="C10">
+            <v>89728</v>
+          </cell>
+          <cell r="E10">
+            <v>100483</v>
+          </cell>
+          <cell r="G10">
+            <v>108389</v>
+          </cell>
+          <cell r="I10">
+            <v>80176</v>
+          </cell>
+          <cell r="K10">
+            <v>86205</v>
+          </cell>
+          <cell r="M10">
+            <v>104123</v>
+          </cell>
+          <cell r="O10">
+            <v>104903</v>
+          </cell>
+          <cell r="Q10">
+            <v>91478</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>5-NorthE</v>
+          </cell>
+          <cell r="C11">
+            <v>77670</v>
+          </cell>
+          <cell r="E11">
+            <v>83917</v>
+          </cell>
+          <cell r="G11">
+            <v>98007</v>
+          </cell>
+          <cell r="I11">
+            <v>78176</v>
+          </cell>
+          <cell r="K11">
+            <v>85661</v>
+          </cell>
+          <cell r="M11">
+            <v>95308</v>
+          </cell>
+          <cell r="O11">
+            <v>100031</v>
+          </cell>
+          <cell r="Q11">
+            <v>99787</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>77670</v>
+          </cell>
+          <cell r="E12">
+            <v>83917</v>
+          </cell>
+          <cell r="G12">
+            <v>98007</v>
+          </cell>
+          <cell r="I12">
+            <v>78176</v>
+          </cell>
+          <cell r="K12">
+            <v>85661</v>
+          </cell>
+          <cell r="M12">
+            <v>95308</v>
+          </cell>
+          <cell r="O12">
+            <v>100031</v>
+          </cell>
+          <cell r="Q12">
+            <v>99787</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>6-South</v>
+          </cell>
+          <cell r="C13">
+            <v>93911</v>
+          </cell>
+          <cell r="E13">
+            <v>98125</v>
+          </cell>
+          <cell r="G13">
+            <v>123668</v>
+          </cell>
+          <cell r="I13">
+            <v>93882</v>
+          </cell>
+          <cell r="K13">
+            <v>100379</v>
+          </cell>
+          <cell r="M13">
+            <v>104470</v>
+          </cell>
+          <cell r="O13">
+            <v>108829</v>
+          </cell>
+          <cell r="Q13">
+            <v>101242</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="C14">
+            <v>93911</v>
+          </cell>
+          <cell r="E14">
+            <v>98125</v>
+          </cell>
+          <cell r="G14">
+            <v>123668</v>
+          </cell>
+          <cell r="I14">
+            <v>93882</v>
+          </cell>
+          <cell r="K14">
+            <v>100379</v>
+          </cell>
+          <cell r="M14">
+            <v>104470</v>
+          </cell>
+          <cell r="O14">
+            <v>108829</v>
+          </cell>
+          <cell r="Q14">
+            <v>101242</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15" t="str">
+            <v>4-North</v>
+          </cell>
+          <cell r="C15">
+            <v>94052</v>
+          </cell>
+          <cell r="E15">
+            <v>103220</v>
+          </cell>
+          <cell r="G15">
+            <v>124516</v>
+          </cell>
+          <cell r="I15">
+            <v>90073</v>
+          </cell>
+          <cell r="K15">
+            <v>100542</v>
+          </cell>
+          <cell r="M15">
+            <v>104712</v>
+          </cell>
+          <cell r="O15">
+            <v>105314</v>
+          </cell>
+          <cell r="Q15">
+            <v>104706</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>94052</v>
+          </cell>
+          <cell r="E16">
+            <v>103220</v>
+          </cell>
+          <cell r="G16">
+            <v>124516</v>
+          </cell>
+          <cell r="I16">
+            <v>90073</v>
+          </cell>
+          <cell r="K16">
+            <v>100542</v>
+          </cell>
+          <cell r="M16">
+            <v>104712</v>
+          </cell>
+          <cell r="O16">
+            <v>105314</v>
+          </cell>
+          <cell r="Q16">
+            <v>104706</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="C17">
+            <v>730288</v>
+          </cell>
+          <cell r="E17">
+            <v>760244</v>
+          </cell>
+          <cell r="G17">
+            <v>882904</v>
+          </cell>
+          <cell r="I17">
+            <v>656838</v>
+          </cell>
+          <cell r="K17">
+            <v>750413</v>
+          </cell>
+          <cell r="M17">
+            <v>824160</v>
+          </cell>
+          <cell r="O17">
+            <v>849303</v>
+          </cell>
+          <cell r="Q17">
+            <v>814791</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="C18">
+            <v>730288</v>
+          </cell>
+          <cell r="E18">
+            <v>760244</v>
+          </cell>
+          <cell r="G18">
+            <v>882904</v>
+          </cell>
+          <cell r="I18">
+            <v>656838</v>
+          </cell>
+          <cell r="K18">
+            <v>750413</v>
+          </cell>
+          <cell r="M18">
+            <v>824160</v>
+          </cell>
+          <cell r="O18">
+            <v>849303</v>
+          </cell>
+          <cell r="Q18">
+            <v>814791</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -54353,4 +55749,1288 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7612BCC-6D3F-4412-AF7A-504EF43B9006}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!C:C)</f>
+        <v>190200</v>
+      </c>
+      <c r="C2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!E:E)</f>
+        <v>219954</v>
+      </c>
+      <c r="D2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!G:G)</f>
+        <v>260272</v>
+      </c>
+      <c r="E2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!I:I)</f>
+        <v>192174</v>
+      </c>
+      <c r="F2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!K:K)</f>
+        <v>214257</v>
+      </c>
+      <c r="G2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!M:M)</f>
+        <v>208327</v>
+      </c>
+      <c r="H2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!O:O)</f>
+        <v>219159</v>
+      </c>
+      <c r="I2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!Q:Q)</f>
+        <v>215373</v>
+      </c>
+      <c r="J2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!S:S)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!U:U)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!W:W)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!Y:Y)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="47">
+        <f>SUM(B2:M2)</f>
+        <v>1719716</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!C:C)</f>
+        <v>160382</v>
+      </c>
+      <c r="C3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!E:E)</f>
+        <v>171181</v>
+      </c>
+      <c r="D3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!G:G)</f>
+        <v>193873</v>
+      </c>
+      <c r="E3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!I:I)</f>
+        <v>131725</v>
+      </c>
+      <c r="F3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!K:K)</f>
+        <v>156343</v>
+      </c>
+      <c r="G3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!M:M)</f>
+        <v>161950</v>
+      </c>
+      <c r="H3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!O:O)</f>
+        <v>175011</v>
+      </c>
+      <c r="I3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!Q:Q)</f>
+        <v>183407</v>
+      </c>
+      <c r="J3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!S:S)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!U:U)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!W:W)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!Y:Y)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="47">
+        <f>SUM(B3:M3)</f>
+        <v>1333872</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!C:C)</f>
+        <v>86684</v>
+      </c>
+      <c r="C4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!E:E)</f>
+        <v>102154</v>
+      </c>
+      <c r="D4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!G:G)</f>
+        <v>115805</v>
+      </c>
+      <c r="E4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!I:I)</f>
+        <v>80877</v>
+      </c>
+      <c r="F4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!K:K)</f>
+        <v>98781</v>
+      </c>
+      <c r="G4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!M:M)</f>
+        <v>90261</v>
+      </c>
+      <c r="H4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!O:O)</f>
+        <v>105339</v>
+      </c>
+      <c r="I4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!Q:Q)</f>
+        <v>94434</v>
+      </c>
+      <c r="J4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!S:S)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!U:U)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!W:W)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!Y:Y)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="47">
+        <f>SUM(B4:M4)</f>
+        <v>774335</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!C:C)</f>
+        <v>92632</v>
+      </c>
+      <c r="C5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!E:E)</f>
+        <v>95678</v>
+      </c>
+      <c r="D5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!G:G)</f>
+        <v>112490</v>
+      </c>
+      <c r="E5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!I:I)</f>
+        <v>73709</v>
+      </c>
+      <c r="F5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!K:K)</f>
+        <v>103374</v>
+      </c>
+      <c r="G5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!M:M)</f>
+        <v>100869</v>
+      </c>
+      <c r="H5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!O:O)</f>
+        <v>92912</v>
+      </c>
+      <c r="I5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!Q:Q)</f>
+        <v>98607</v>
+      </c>
+      <c r="J5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!S:S)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!U:U)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!W:W)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!Y:Y)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="47">
+        <f>SUM(B5:M5)</f>
+        <v>770271</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!C:C)</f>
+        <v>69073</v>
+      </c>
+      <c r="C6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!E:E)</f>
+        <v>73598</v>
+      </c>
+      <c r="D6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!G:G)</f>
+        <v>99432</v>
+      </c>
+      <c r="E6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!I:I)</f>
+        <v>68047</v>
+      </c>
+      <c r="F6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!K:K)</f>
+        <v>67717</v>
+      </c>
+      <c r="G6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!M:M)</f>
+        <v>70374</v>
+      </c>
+      <c r="H6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!O:O)</f>
+        <v>73141</v>
+      </c>
+      <c r="I6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!Q:Q)</f>
+        <v>66304</v>
+      </c>
+      <c r="J6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!S:S)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!U:U)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!W:W)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!Y:Y)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="47">
+        <f>SUM(B6:M6)</f>
+        <v>587686</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="46" t="s">
+        <v>599</v>
+      </c>
+      <c r="B7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!C:C)</f>
+        <v>90495</v>
+      </c>
+      <c r="C7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!E:E)</f>
+        <v>87159</v>
+      </c>
+      <c r="D7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!G:G)</f>
+        <v>100721</v>
+      </c>
+      <c r="E7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!I:I)</f>
+        <v>74766</v>
+      </c>
+      <c r="F7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!K:K)</f>
+        <v>85556</v>
+      </c>
+      <c r="G7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!M:M)</f>
+        <v>88261</v>
+      </c>
+      <c r="H7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!O:O)</f>
+        <v>90419</v>
+      </c>
+      <c r="I7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!Q:Q)</f>
+        <v>99113</v>
+      </c>
+      <c r="J7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!S:S)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!U:U)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!W:W)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!Y:Y)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="47">
+        <f>SUM(B7:M7)</f>
+        <v>716490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B8" s="47">
+        <f>SUM(B2:B7)</f>
+        <v>689466</v>
+      </c>
+      <c r="C8" s="47">
+        <f>SUM(C2:C7)</f>
+        <v>749724</v>
+      </c>
+      <c r="D8" s="47">
+        <f>SUM(D2:D7)</f>
+        <v>882593</v>
+      </c>
+      <c r="E8" s="47">
+        <f>SUM(E2:E7)</f>
+        <v>621298</v>
+      </c>
+      <c r="F8" s="47">
+        <f>SUM(F2:F7)</f>
+        <v>726028</v>
+      </c>
+      <c r="G8" s="47">
+        <f>SUM(G2:G7)</f>
+        <v>720042</v>
+      </c>
+      <c r="H8" s="47">
+        <f>SUM(H2:H7)</f>
+        <v>755981</v>
+      </c>
+      <c r="I8" s="47">
+        <f>SUM(I2:I7)</f>
+        <v>757238</v>
+      </c>
+      <c r="J8" s="47">
+        <f>SUM(J2:J7)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="47">
+        <f>SUM(K2:K7)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="47">
+        <f>SUM(L2:L7)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="47">
+        <f>SUM(M2:M7)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="47">
+        <f>SUM(N2:N7)</f>
+        <v>5902370</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800480D2-A47D-4B4E-BC6F-84CB2036ED0B}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!D:D)</f>
+        <v>214300</v>
+      </c>
+      <c r="C2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!F:F)</f>
+        <v>239200</v>
+      </c>
+      <c r="D2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!H:H)</f>
+        <v>265100</v>
+      </c>
+      <c r="E2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!J:J)</f>
+        <v>175100</v>
+      </c>
+      <c r="F2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!L:L)</f>
+        <v>211400</v>
+      </c>
+      <c r="G2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!N:N)</f>
+        <v>234300</v>
+      </c>
+      <c r="H2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!P:P)</f>
+        <v>239300</v>
+      </c>
+      <c r="I2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!R:R)</f>
+        <v>214500</v>
+      </c>
+      <c r="J2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!T:T)</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!V:V)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!X:X)</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A2,'[1]CPAC 2026-WEB'!Z:Z)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="47">
+        <f>SUM(B2:M2)</f>
+        <v>1793200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!D:D)</f>
+        <v>149850</v>
+      </c>
+      <c r="C3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!F:F)</f>
+        <v>158950</v>
+      </c>
+      <c r="D3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!H:H)</f>
+        <v>175470</v>
+      </c>
+      <c r="E3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!J:J)</f>
+        <v>136800</v>
+      </c>
+      <c r="F3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!L:L)</f>
+        <v>169370</v>
+      </c>
+      <c r="G3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!N:N)</f>
+        <v>178420</v>
+      </c>
+      <c r="H3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!P:P)</f>
+        <v>184340</v>
+      </c>
+      <c r="I3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!R:R)</f>
+        <v>185770</v>
+      </c>
+      <c r="J3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!T:T)</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!V:V)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!X:X)</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A3,'[1]CPAC 2026-WEB'!Z:Z)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="47">
+        <f>SUM(B3:M3)</f>
+        <v>1338970</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!D:D)</f>
+        <v>83500</v>
+      </c>
+      <c r="C4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!F:F)</f>
+        <v>88000</v>
+      </c>
+      <c r="D4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!H:H)</f>
+        <v>95100</v>
+      </c>
+      <c r="E4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!J:J)</f>
+        <v>73700</v>
+      </c>
+      <c r="F4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!L:L)</f>
+        <v>96200</v>
+      </c>
+      <c r="G4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!N:N)</f>
+        <v>91700</v>
+      </c>
+      <c r="H4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!P:P)</f>
+        <v>96500</v>
+      </c>
+      <c r="I4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!R:R)</f>
+        <v>93200</v>
+      </c>
+      <c r="J4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!T:T)</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!V:V)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!X:X)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A4,'[1]CPAC 2026-WEB'!Z:Z)</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="47">
+        <f>SUM(B4:M4)</f>
+        <v>717900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!D:D)</f>
+        <v>97150</v>
+      </c>
+      <c r="C5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!F:F)</f>
+        <v>99150</v>
+      </c>
+      <c r="D5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!H:H)</f>
+        <v>113800</v>
+      </c>
+      <c r="E5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!J:J)</f>
+        <v>80600</v>
+      </c>
+      <c r="F5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!L:L)</f>
+        <v>96300</v>
+      </c>
+      <c r="G5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!N:N)</f>
+        <v>100400</v>
+      </c>
+      <c r="H5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!P:P)</f>
+        <v>100550</v>
+      </c>
+      <c r="I5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!R:R)</f>
+        <v>94100</v>
+      </c>
+      <c r="J5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!T:T)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!V:V)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!X:X)</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A5,'[1]CPAC 2026-WEB'!Z:Z)</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="47">
+        <f>SUM(B5:M5)</f>
+        <v>782050</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!D:D)</f>
+        <v>83225</v>
+      </c>
+      <c r="C6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!F:F)</f>
+        <v>83925</v>
+      </c>
+      <c r="D6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!H:H)</f>
+        <v>92889</v>
+      </c>
+      <c r="E6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!J:J)</f>
+        <v>76954</v>
+      </c>
+      <c r="F6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!L:L)</f>
+        <v>84370</v>
+      </c>
+      <c r="G6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!N:N)</f>
+        <v>84225</v>
+      </c>
+      <c r="H6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!P:P)</f>
+        <v>86925</v>
+      </c>
+      <c r="I6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!R:R)</f>
+        <v>87025</v>
+      </c>
+      <c r="J6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!T:T)</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!V:V)</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!X:X)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A6,'[1]CPAC 2026-WEB'!Z:Z)</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="47">
+        <f>SUM(B6:M6)</f>
+        <v>679538</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="46" t="s">
+        <v>599</v>
+      </c>
+      <c r="B7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!D:D)</f>
+        <v>93800</v>
+      </c>
+      <c r="C7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!F:F)</f>
+        <v>94700</v>
+      </c>
+      <c r="D7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!H:H)</f>
+        <v>107900</v>
+      </c>
+      <c r="E7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!J:J)</f>
+        <v>91600</v>
+      </c>
+      <c r="F7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!L:L)</f>
+        <v>104000</v>
+      </c>
+      <c r="G7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!N:N)</f>
+        <v>102200</v>
+      </c>
+      <c r="H7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!P:P)</f>
+        <v>103800</v>
+      </c>
+      <c r="I7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!R:R)</f>
+        <v>100900</v>
+      </c>
+      <c r="J7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!T:T)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!V:V)</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!X:X)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="47">
+        <f>SUMIF('[1]CPAC 2026-WEB'!$A:$A,$A7,'[1]CPAC 2026-WEB'!Z:Z)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="47">
+        <f>SUM(B7:M7)</f>
+        <v>798900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B8" s="47">
+        <f>SUM(B2:B7)</f>
+        <v>721825</v>
+      </c>
+      <c r="C8" s="47">
+        <f>SUM(C2:C7)</f>
+        <v>763925</v>
+      </c>
+      <c r="D8" s="47">
+        <f>SUM(D2:D7)</f>
+        <v>850259</v>
+      </c>
+      <c r="E8" s="47">
+        <f>SUM(E2:E7)</f>
+        <v>634754</v>
+      </c>
+      <c r="F8" s="47">
+        <f>SUM(F2:F7)</f>
+        <v>761640</v>
+      </c>
+      <c r="G8" s="47">
+        <f>SUM(G2:G7)</f>
+        <v>791245</v>
+      </c>
+      <c r="H8" s="47">
+        <f>SUM(H2:H7)</f>
+        <v>811415</v>
+      </c>
+      <c r="I8" s="47">
+        <f>SUM(I2:I7)</f>
+        <v>775495</v>
+      </c>
+      <c r="J8" s="47">
+        <f>SUM(J2:J7)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="47">
+        <f>SUM(K2:K7)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="47">
+        <f>SUM(L2:L7)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="47">
+        <f>SUM(M2:M7)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="47">
+        <f>SUM(N2:N7)</f>
+        <v>6110558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52355496-F79B-4896-B284-DB9209C1997D}">
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.08984375" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="8.7265625" style="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" s="46" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="46" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="46" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="46" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A2,'[1]CPAC 2025-WEB'!C:C)</f>
+        <v>200099</v>
+      </c>
+      <c r="C2" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A2,'[1]CPAC 2025-WEB'!E:E)</f>
+        <v>208536</v>
+      </c>
+      <c r="D2" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A2,'[1]CPAC 2025-WEB'!G:G)</f>
+        <v>239658</v>
+      </c>
+      <c r="E2" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A2,'[1]CPAC 2025-WEB'!I:I)</f>
+        <v>175649</v>
+      </c>
+      <c r="F2" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A2,'[1]CPAC 2025-WEB'!K:K)</f>
+        <v>212577</v>
+      </c>
+      <c r="G2" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A2,'[1]CPAC 2025-WEB'!M:M)</f>
+        <v>236605</v>
+      </c>
+      <c r="H2" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A2,'[1]CPAC 2025-WEB'!O:O)</f>
+        <v>228963</v>
+      </c>
+      <c r="I2" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A2,'[1]CPAC 2025-WEB'!Q:Q)</f>
+        <v>232783</v>
+      </c>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47">
+        <f>SUM(B2:M2)</f>
+        <v>1734870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A3,'[1]CPAC 2025-WEB'!C:C)</f>
+        <v>174828</v>
+      </c>
+      <c r="C3" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A3,'[1]CPAC 2025-WEB'!E:E)</f>
+        <v>165963</v>
+      </c>
+      <c r="D3" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A3,'[1]CPAC 2025-WEB'!G:G)</f>
+        <v>188666</v>
+      </c>
+      <c r="E3" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A3,'[1]CPAC 2025-WEB'!I:I)</f>
+        <v>138881</v>
+      </c>
+      <c r="F3" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A3,'[1]CPAC 2025-WEB'!K:K)</f>
+        <v>165051</v>
+      </c>
+      <c r="G3" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A3,'[1]CPAC 2025-WEB'!M:M)</f>
+        <v>178943</v>
+      </c>
+      <c r="H3" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A3,'[1]CPAC 2025-WEB'!O:O)</f>
+        <v>201263</v>
+      </c>
+      <c r="I3" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A3,'[1]CPAC 2025-WEB'!Q:Q)</f>
+        <v>184795</v>
+      </c>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47">
+        <f>SUM(B3:M3)</f>
+        <v>1398390</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A4,'[1]CPAC 2025-WEB'!C:C)</f>
+        <v>89728</v>
+      </c>
+      <c r="C4" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A4,'[1]CPAC 2025-WEB'!E:E)</f>
+        <v>100483</v>
+      </c>
+      <c r="D4" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A4,'[1]CPAC 2025-WEB'!G:G)</f>
+        <v>108389</v>
+      </c>
+      <c r="E4" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A4,'[1]CPAC 2025-WEB'!I:I)</f>
+        <v>80176</v>
+      </c>
+      <c r="F4" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A4,'[1]CPAC 2025-WEB'!K:K)</f>
+        <v>86205</v>
+      </c>
+      <c r="G4" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A4,'[1]CPAC 2025-WEB'!M:M)</f>
+        <v>104123</v>
+      </c>
+      <c r="H4" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A4,'[1]CPAC 2025-WEB'!O:O)</f>
+        <v>104903</v>
+      </c>
+      <c r="I4" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A4,'[1]CPAC 2025-WEB'!Q:Q)</f>
+        <v>91478</v>
+      </c>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47">
+        <f>SUM(B4:M4)</f>
+        <v>765485</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="B5" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A5,'[1]CPAC 2025-WEB'!C:C)</f>
+        <v>94052</v>
+      </c>
+      <c r="C5" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A5,'[1]CPAC 2025-WEB'!E:E)</f>
+        <v>103220</v>
+      </c>
+      <c r="D5" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A5,'[1]CPAC 2025-WEB'!G:G)</f>
+        <v>124516</v>
+      </c>
+      <c r="E5" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A5,'[1]CPAC 2025-WEB'!I:I)</f>
+        <v>90073</v>
+      </c>
+      <c r="F5" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A5,'[1]CPAC 2025-WEB'!K:K)</f>
+        <v>100542</v>
+      </c>
+      <c r="G5" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A5,'[1]CPAC 2025-WEB'!M:M)</f>
+        <v>104712</v>
+      </c>
+      <c r="H5" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A5,'[1]CPAC 2025-WEB'!O:O)</f>
+        <v>105314</v>
+      </c>
+      <c r="I5" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A5,'[1]CPAC 2025-WEB'!Q:Q)</f>
+        <v>104706</v>
+      </c>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47">
+        <f>SUM(B5:M5)</f>
+        <v>827135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="46" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A6,'[1]CPAC 2025-WEB'!C:C)</f>
+        <v>77670</v>
+      </c>
+      <c r="C6" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A6,'[1]CPAC 2025-WEB'!E:E)</f>
+        <v>83917</v>
+      </c>
+      <c r="D6" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A6,'[1]CPAC 2025-WEB'!G:G)</f>
+        <v>98007</v>
+      </c>
+      <c r="E6" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A6,'[1]CPAC 2025-WEB'!I:I)</f>
+        <v>78176</v>
+      </c>
+      <c r="F6" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A6,'[1]CPAC 2025-WEB'!K:K)</f>
+        <v>85661</v>
+      </c>
+      <c r="G6" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A6,'[1]CPAC 2025-WEB'!M:M)</f>
+        <v>95308</v>
+      </c>
+      <c r="H6" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A6,'[1]CPAC 2025-WEB'!O:O)</f>
+        <v>100031</v>
+      </c>
+      <c r="I6" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A6,'[1]CPAC 2025-WEB'!Q:Q)</f>
+        <v>99787</v>
+      </c>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47">
+        <f>SUM(B6:M6)</f>
+        <v>718557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="46" t="s">
+        <v>599</v>
+      </c>
+      <c r="B7" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A7,'[1]CPAC 2025-WEB'!C:C)</f>
+        <v>93911</v>
+      </c>
+      <c r="C7" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A7,'[1]CPAC 2025-WEB'!E:E)</f>
+        <v>98125</v>
+      </c>
+      <c r="D7" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A7,'[1]CPAC 2025-WEB'!G:G)</f>
+        <v>123668</v>
+      </c>
+      <c r="E7" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A7,'[1]CPAC 2025-WEB'!I:I)</f>
+        <v>93882</v>
+      </c>
+      <c r="F7" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A7,'[1]CPAC 2025-WEB'!K:K)</f>
+        <v>100379</v>
+      </c>
+      <c r="G7" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A7,'[1]CPAC 2025-WEB'!M:M)</f>
+        <v>104470</v>
+      </c>
+      <c r="H7" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A7,'[1]CPAC 2025-WEB'!O:O)</f>
+        <v>108829</v>
+      </c>
+      <c r="I7" s="47">
+        <f>SUMIF('[1]CPAC 2025-WEB'!$A:$A,$A7,'[1]CPAC 2025-WEB'!Q:Q)</f>
+        <v>101242</v>
+      </c>
+      <c r="J7" s="47"/>
+      <c r="K7" s="47"/>
+      <c r="L7" s="47"/>
+      <c r="M7" s="47"/>
+      <c r="N7" s="47">
+        <f>SUM(B7:M7)</f>
+        <v>824506</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B8" s="47">
+        <f>SUM(B2:B7)</f>
+        <v>730288</v>
+      </c>
+      <c r="C8" s="47">
+        <f>SUM(C2:C7)</f>
+        <v>760244</v>
+      </c>
+      <c r="D8" s="47">
+        <f>SUM(D2:D7)</f>
+        <v>882904</v>
+      </c>
+      <c r="E8" s="47">
+        <f>SUM(E2:E7)</f>
+        <v>656837</v>
+      </c>
+      <c r="F8" s="47">
+        <f>SUM(F2:F7)</f>
+        <v>750415</v>
+      </c>
+      <c r="G8" s="47">
+        <f>SUM(G2:G7)</f>
+        <v>824161</v>
+      </c>
+      <c r="H8" s="47">
+        <f>SUM(H2:H7)</f>
+        <v>849303</v>
+      </c>
+      <c r="I8" s="47">
+        <f>SUM(I2:I7)</f>
+        <v>814791</v>
+      </c>
+      <c r="J8" s="47">
+        <f>SUM(J2:J7)</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="47">
+        <f>SUM(K2:K7)</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="47">
+        <f>SUM(L2:L7)</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="47">
+        <f>SUM(M2:M7)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="47">
+        <f>SUM(N2:N7)</f>
+        <v>6268943</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>